--- a/Result/profitability/2743.xlsx
+++ b/Result/profitability/2743.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM43"/>
+  <dimension ref="A1:AM44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5891,6 +5891,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1616</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1473</v>
+      </c>
+      <c r="E44" t="n">
+        <v>143</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="G44" t="n">
+        <v>25</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>28</v>
+      </c>
+      <c r="K44" t="n">
+        <v>28</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.04625</v>
+      </c>
+      <c r="N44" t="n">
+        <v>11.59125</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-0.6432748538011697</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-0.2845594179466451</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-1.417808219178082</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>-0.00895856662933936</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
